--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753910</v>
+        <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>92626</v>
+        <v>80152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742161</v>
+        <v>742037</v>
       </c>
       <c r="R9" t="n">
-        <v>7154742</v>
+        <v>7154881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,32 +1495,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753908</v>
+        <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>92626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742037</v>
+        <v>742161</v>
       </c>
       <c r="R10" t="n">
-        <v>7154881</v>
+        <v>7154742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753942</v>
+        <v>127753900</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,34 +2004,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741967</v>
+        <v>741768</v>
       </c>
       <c r="R15" t="n">
-        <v>7154801</v>
+        <v>7154679</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,6 +2072,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2090,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753889</v>
+        <v>127753942</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742160</v>
+        <v>741967</v>
       </c>
       <c r="R16" t="n">
-        <v>7154588</v>
+        <v>7154801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753900</v>
+        <v>127753889</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,42 +2211,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741768</v>
+        <v>742160</v>
       </c>
       <c r="R17" t="n">
-        <v>7154679</v>
+        <v>7154588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,11 +2271,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753919</v>
+        <v>127753940</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R22" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753940</v>
+        <v>127753919</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R23" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2981,53 +2981,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753902</v>
+        <v>127753949</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741941</v>
+        <v>742157</v>
       </c>
       <c r="R25" t="n">
-        <v>7154765</v>
+        <v>7154655</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,11 +3052,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3091,45 +3078,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753949</v>
+        <v>127753902</v>
       </c>
       <c r="B26" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742157</v>
+        <v>741941</v>
       </c>
       <c r="R26" t="n">
-        <v>7154655</v>
+        <v>7154765</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,6 +3157,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3973,10 +3973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753904</v>
+        <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,42 +3984,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741989</v>
+        <v>741961</v>
       </c>
       <c r="R35" t="n">
-        <v>7154834</v>
+        <v>7154435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,11 +4044,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4083,10 +4070,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753934</v>
+        <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,34 +4081,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741961</v>
+        <v>741989</v>
       </c>
       <c r="R36" t="n">
-        <v>7154435</v>
+        <v>7154834</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4154,6 +4149,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4277,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753944</v>
+        <v>127753947</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>742023</v>
+        <v>741968</v>
       </c>
       <c r="R38" t="n">
-        <v>7154856</v>
+        <v>7154662</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4374,45 +4374,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753947</v>
+        <v>127753901</v>
       </c>
       <c r="B39" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741968</v>
+        <v>741759</v>
       </c>
       <c r="R39" t="n">
-        <v>7154662</v>
+        <v>7154728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,6 +4453,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4471,7 +4484,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753901</v>
+        <v>127753893</v>
       </c>
       <c r="B40" t="n">
         <v>57663</v>
@@ -4504,7 +4517,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4514,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741759</v>
+        <v>742157</v>
       </c>
       <c r="R40" t="n">
-        <v>7154728</v>
+        <v>7154690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4554,7 +4567,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4581,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753893</v>
+        <v>127753914</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>78779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4592,42 +4605,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742157</v>
+        <v>741905</v>
       </c>
       <c r="R41" t="n">
-        <v>7154690</v>
+        <v>7154732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4662,17 +4667,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4691,10 +4692,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753914</v>
+        <v>127753944</v>
       </c>
       <c r="B42" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4702,21 +4703,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4726,10 +4727,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741905</v>
+        <v>742023</v>
       </c>
       <c r="R42" t="n">
-        <v>7154732</v>
+        <v>7154856</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4770,7 +4771,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753888</v>
+        <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742028</v>
+        <v>741946</v>
       </c>
       <c r="R47" t="n">
-        <v>7154827</v>
+        <v>7154636</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753927</v>
+        <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741946</v>
+        <v>742091</v>
       </c>
       <c r="R48" t="n">
-        <v>7154636</v>
+        <v>7154655</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753917</v>
+        <v>127753915</v>
       </c>
       <c r="B49" t="n">
         <v>78778</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742091</v>
+        <v>742161</v>
       </c>
       <c r="R49" t="n">
-        <v>7154655</v>
+        <v>7154587</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753915</v>
+        <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>78778</v>
+        <v>79052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742161</v>
+        <v>742028</v>
       </c>
       <c r="R50" t="n">
-        <v>7154587</v>
+        <v>7154827</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,32 +5578,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127753912</v>
+        <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>92634</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742158</v>
+        <v>742030</v>
       </c>
       <c r="R51" t="n">
-        <v>7154703</v>
+        <v>7154816</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127753945</v>
+        <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5686,21 +5686,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>742030</v>
+        <v>741905</v>
       </c>
       <c r="R52" t="n">
-        <v>7154816</v>
+        <v>7154732</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127753890</v>
+        <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5783,21 +5783,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741905</v>
+        <v>741791</v>
       </c>
       <c r="R53" t="n">
-        <v>7154732</v>
+        <v>7154734</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5843,6 +5843,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5869,7 +5874,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127753938</v>
+        <v>127753929</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -5904,10 +5909,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741791</v>
+        <v>742148</v>
       </c>
       <c r="R54" t="n">
-        <v>7154734</v>
+        <v>7154762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,11 +5945,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5971,32 +5971,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127753929</v>
+        <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>92634</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>742148</v>
+        <v>742158</v>
       </c>
       <c r="R55" t="n">
-        <v>7154762</v>
+        <v>7154703</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1199,32 +1199,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753946</v>
+        <v>127753910</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742105</v>
+        <v>742161</v>
       </c>
       <c r="R7" t="n">
-        <v>7154699</v>
+        <v>7154742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1270,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753921</v>
+        <v>127753946</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1336,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742101</v>
+        <v>742105</v>
       </c>
       <c r="R8" t="n">
-        <v>7154742</v>
+        <v>7154699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1367,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753908</v>
+        <v>127753921</v>
       </c>
       <c r="B9" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742037</v>
+        <v>742101</v>
       </c>
       <c r="R9" t="n">
-        <v>7154881</v>
+        <v>7154742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,32 +1495,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753910</v>
+        <v>127753908</v>
       </c>
       <c r="B10" t="n">
-        <v>92626</v>
+        <v>80152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742161</v>
+        <v>742037</v>
       </c>
       <c r="R10" t="n">
-        <v>7154742</v>
+        <v>7154881</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753936</v>
+        <v>127753887</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741761</v>
+        <v>741864</v>
       </c>
       <c r="R11" t="n">
-        <v>7154695</v>
+        <v>7154736</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753887</v>
+        <v>127753894</v>
       </c>
       <c r="B12" t="n">
-        <v>79052</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,34 +1700,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741864</v>
+        <v>742156</v>
       </c>
       <c r="R12" t="n">
-        <v>7154736</v>
+        <v>7154631</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1768,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753894</v>
+        <v>127753936</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,42 +1810,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742156</v>
+        <v>741761</v>
       </c>
       <c r="R13" t="n">
-        <v>7154631</v>
+        <v>7154695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,11 +1870,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753948</v>
+        <v>127753942</v>
       </c>
       <c r="B14" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742148</v>
+        <v>741967</v>
       </c>
       <c r="R14" t="n">
-        <v>7154762</v>
+        <v>7154801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753900</v>
+        <v>127753889</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,42 +2004,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741768</v>
+        <v>742160</v>
       </c>
       <c r="R15" t="n">
-        <v>7154679</v>
+        <v>7154588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,11 +2064,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2090,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753942</v>
+        <v>127753930</v>
       </c>
       <c r="B16" t="n">
         <v>79020</v>
@@ -2138,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741967</v>
+        <v>742153</v>
       </c>
       <c r="R16" t="n">
-        <v>7154801</v>
+        <v>7154757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753889</v>
+        <v>127753900</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,34 +2198,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742160</v>
+        <v>741768</v>
       </c>
       <c r="R17" t="n">
-        <v>7154588</v>
+        <v>7154679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,6 +2266,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,32 +2297,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753930</v>
+        <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742153</v>
+        <v>742148</v>
       </c>
       <c r="R18" t="n">
-        <v>7154757</v>
+        <v>7154762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753940</v>
+        <v>127753919</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R22" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2756,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753919</v>
+        <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R23" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2853,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127753916</v>
+        <v>127753902</v>
       </c>
       <c r="B24" t="n">
-        <v>78778</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,34 +2895,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>742075</v>
+        <v>741941</v>
       </c>
       <c r="R24" t="n">
-        <v>7154759</v>
+        <v>7154765</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2963,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2981,32 +2994,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753949</v>
+        <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742157</v>
+        <v>742075</v>
       </c>
       <c r="R25" t="n">
-        <v>7154655</v>
+        <v>7154759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,53 +3091,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753902</v>
+        <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>92628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741941</v>
+        <v>742157</v>
       </c>
       <c r="R26" t="n">
-        <v>7154765</v>
+        <v>7154655</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,11 +3162,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91162</v>
+        <v>91168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127753918</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4277,45 +4277,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753947</v>
+        <v>127753901</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741968</v>
+        <v>741759</v>
       </c>
       <c r="R38" t="n">
-        <v>7154662</v>
+        <v>7154728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,6 +4356,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,7 +4387,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753901</v>
+        <v>127753893</v>
       </c>
       <c r="B39" t="n">
         <v>57663</v>
@@ -4407,7 +4420,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4417,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741759</v>
+        <v>742157</v>
       </c>
       <c r="R39" t="n">
-        <v>7154728</v>
+        <v>7154690</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4457,7 +4470,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4484,10 +4497,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753893</v>
+        <v>127753944</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4495,42 +4508,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742157</v>
+        <v>742023</v>
       </c>
       <c r="R40" t="n">
-        <v>7154690</v>
+        <v>7154856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,11 +4568,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753914</v>
+        <v>127753939</v>
       </c>
       <c r="B41" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,34 +4605,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741905</v>
+        <v>741814</v>
       </c>
       <c r="R41" t="n">
-        <v>7154732</v>
+        <v>7154740</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4672,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4692,32 +4704,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753944</v>
+        <v>127753947</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4727,10 +4739,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>742023</v>
+        <v>741968</v>
       </c>
       <c r="R42" t="n">
-        <v>7154856</v>
+        <v>7154662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,10 +4801,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753939</v>
+        <v>127753914</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4800,41 +4812,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741814</v>
+        <v>741905</v>
       </c>
       <c r="R43" t="n">
-        <v>7154740</v>
+        <v>7154732</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,11 +4872,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753915</v>
+        <v>127753888</v>
       </c>
       <c r="B49" t="n">
-        <v>78778</v>
+        <v>79052</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742161</v>
+        <v>742028</v>
       </c>
       <c r="R49" t="n">
-        <v>7154587</v>
+        <v>7154827</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753888</v>
+        <v>127753915</v>
       </c>
       <c r="B50" t="n">
-        <v>79052</v>
+        <v>78778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742028</v>
+        <v>742161</v>
       </c>
       <c r="R50" t="n">
-        <v>7154827</v>
+        <v>7154587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5974,7 +5974,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753899</v>
+        <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741764</v>
+        <v>742082</v>
       </c>
       <c r="R2" t="n">
-        <v>7154654</v>
+        <v>7154435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753896</v>
+        <v>127753899</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742082</v>
+        <v>741764</v>
       </c>
       <c r="R3" t="n">
-        <v>7154435</v>
+        <v>7154654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>127753903</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>127753910</v>
       </c>
       <c r="B7" t="n">
-        <v>92632</v>
+        <v>92635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127753946</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>127753921</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127753908</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>127753887</v>
       </c>
       <c r="B11" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>127753894</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127753936</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>127753942</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127753889</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>127753930</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>127753900</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127753924</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127753943</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>127753892</v>
       </c>
       <c r="B21" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753919</v>
+        <v>127753940</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R22" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753940</v>
+        <v>127753919</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>91359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R23" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127753902</v>
+        <v>127753916</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>78781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,42 +2895,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741941</v>
+        <v>742075</v>
       </c>
       <c r="R24" t="n">
-        <v>7154765</v>
+        <v>7154759</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,11 +2955,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2994,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753916</v>
+        <v>127753902</v>
       </c>
       <c r="B25" t="n">
-        <v>78778</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,34 +2992,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742075</v>
+        <v>741941</v>
       </c>
       <c r="R25" t="n">
-        <v>7154759</v>
+        <v>7154765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3065,6 +3060,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3094,7 +3094,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91168</v>
+        <v>91171</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>127753923</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127753918</v>
       </c>
       <c r="B34" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753901</v>
+        <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4288,42 +4288,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741759</v>
+        <v>742023</v>
       </c>
       <c r="R38" t="n">
-        <v>7154728</v>
+        <v>7154856</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4356,11 +4348,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753893</v>
+        <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4398,29 +4385,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4430,10 +4416,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>742157</v>
+        <v>741814</v>
       </c>
       <c r="R39" t="n">
-        <v>7154690</v>
+        <v>7154740</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,7 +4456,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4479,6 +4465,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4497,10 +4484,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753944</v>
+        <v>127753893</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4508,34 +4495,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742023</v>
+        <v>742157</v>
       </c>
       <c r="R40" t="n">
-        <v>7154856</v>
+        <v>7154690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4568,6 +4563,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753939</v>
+        <v>127753901</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,28 +4605,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4636,10 +4637,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741814</v>
+        <v>741759</v>
       </c>
       <c r="R41" t="n">
-        <v>7154740</v>
+        <v>7154728</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4676,7 +4677,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4685,7 +4686,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>127753947</v>
       </c>
       <c r="B42" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>127753914</v>
       </c>
       <c r="B43" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127753891</v>
+        <v>127753906</v>
       </c>
       <c r="B44" t="n">
-        <v>79638</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742075</v>
+        <v>742078</v>
       </c>
       <c r="R44" t="n">
-        <v>7154759</v>
+        <v>7154651</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127753906</v>
+        <v>127753891</v>
       </c>
       <c r="B45" t="n">
-        <v>57823</v>
+        <v>79641</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742078</v>
+        <v>742075</v>
       </c>
       <c r="R45" t="n">
-        <v>7154651</v>
+        <v>7154759</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753888</v>
+        <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>79052</v>
+        <v>78781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742028</v>
+        <v>742161</v>
       </c>
       <c r="R49" t="n">
-        <v>7154827</v>
+        <v>7154587</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753915</v>
+        <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>78778</v>
+        <v>79055</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742161</v>
+        <v>742028</v>
       </c>
       <c r="R50" t="n">
-        <v>7154587</v>
+        <v>7154827</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127753899</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127753903</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>127753910</v>
       </c>
       <c r="B7" t="n">
-        <v>92635</v>
+        <v>92643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753946</v>
+        <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742105</v>
+        <v>742101</v>
       </c>
       <c r="R8" t="n">
-        <v>7154699</v>
+        <v>7154742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,11 +1367,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,32 +1393,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753921</v>
+        <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>80161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742101</v>
+        <v>742037</v>
       </c>
       <c r="R9" t="n">
-        <v>7154742</v>
+        <v>7154881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,32 +1490,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753908</v>
+        <v>127753946</v>
       </c>
       <c r="B10" t="n">
-        <v>80155</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742037</v>
+        <v>742105</v>
       </c>
       <c r="R10" t="n">
-        <v>7154881</v>
+        <v>7154699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,7 +1595,7 @@
         <v>127753887</v>
       </c>
       <c r="B11" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753894</v>
+        <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,42 +1700,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742156</v>
+        <v>741761</v>
       </c>
       <c r="R12" t="n">
-        <v>7154631</v>
+        <v>7154695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753936</v>
+        <v>127753894</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,34 +1797,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741761</v>
+        <v>742156</v>
       </c>
       <c r="R13" t="n">
-        <v>7154695</v>
+        <v>7154631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,6 +1865,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753942</v>
+        <v>127753948</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741967</v>
+        <v>742148</v>
       </c>
       <c r="R14" t="n">
-        <v>7154801</v>
+        <v>7154762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
         <v>127753889</v>
       </c>
       <c r="B15" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753930</v>
+        <v>127753942</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742153</v>
+        <v>741967</v>
       </c>
       <c r="R16" t="n">
-        <v>7154757</v>
+        <v>7154801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753900</v>
+        <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,42 +2198,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741768</v>
+        <v>742153</v>
       </c>
       <c r="R17" t="n">
-        <v>7154679</v>
+        <v>7154757</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,11 +2258,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,45 +2284,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753948</v>
+        <v>127753900</v>
       </c>
       <c r="B18" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742148</v>
+        <v>741768</v>
       </c>
       <c r="R18" t="n">
-        <v>7154762</v>
+        <v>7154679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,6 +2363,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753924</v>
+        <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>91367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753943</v>
+        <v>127753892</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742046</v>
+        <v>742068</v>
       </c>
       <c r="R20" t="n">
-        <v>7154883</v>
+        <v>7154593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753892</v>
+        <v>127753940</v>
       </c>
       <c r="B21" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742068</v>
+        <v>741843</v>
       </c>
       <c r="R21" t="n">
-        <v>7154593</v>
+        <v>7154744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753940</v>
+        <v>127753924</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R22" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2761,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753919</v>
+        <v>127753943</v>
       </c>
       <c r="B23" t="n">
-        <v>91359</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742028</v>
+        <v>742046</v>
       </c>
       <c r="R23" t="n">
-        <v>7154827</v>
+        <v>7154883</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>127753916</v>
       </c>
       <c r="B24" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,53 +2981,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753902</v>
+        <v>127753949</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741941</v>
+        <v>742157</v>
       </c>
       <c r="R25" t="n">
-        <v>7154765</v>
+        <v>7154655</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,11 +3052,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3091,45 +3078,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753949</v>
+        <v>127753902</v>
       </c>
       <c r="B26" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742157</v>
+        <v>741941</v>
       </c>
       <c r="R26" t="n">
-        <v>7154655</v>
+        <v>7154765</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,6 +3157,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91171</v>
+        <v>91179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753928</v>
+        <v>127753926</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741972</v>
+        <v>741971</v>
       </c>
       <c r="R28" t="n">
-        <v>7154672</v>
+        <v>7154589</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753937</v>
+        <v>127753922</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741770</v>
+        <v>741952</v>
       </c>
       <c r="R29" t="n">
-        <v>7154740</v>
+        <v>7154778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127753922</v>
+        <v>127753937</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741952</v>
+        <v>741770</v>
       </c>
       <c r="R31" t="n">
-        <v>7154778</v>
+        <v>7154740</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127753926</v>
+        <v>127753928</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741971</v>
+        <v>741972</v>
       </c>
       <c r="R32" t="n">
-        <v>7154589</v>
+        <v>7154672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3782,7 +3782,7 @@
         <v>127753923</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127753918</v>
       </c>
       <c r="B34" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4277,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753944</v>
+        <v>127753947</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>742023</v>
+        <v>741968</v>
       </c>
       <c r="R38" t="n">
-        <v>7154856</v>
+        <v>7154662</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4377,7 +4377,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753893</v>
+        <v>127753944</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4495,42 +4495,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742157</v>
+        <v>742023</v>
       </c>
       <c r="R40" t="n">
-        <v>7154690</v>
+        <v>7154856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,11 +4555,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4581,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753901</v>
+        <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4627,7 +4614,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4637,10 +4624,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741759</v>
+        <v>742157</v>
       </c>
       <c r="R41" t="n">
-        <v>7154728</v>
+        <v>7154690</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,7 +4664,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4704,45 +4691,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753947</v>
+        <v>127753901</v>
       </c>
       <c r="B42" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741968</v>
+        <v>741759</v>
       </c>
       <c r="R42" t="n">
-        <v>7154662</v>
+        <v>7154728</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4775,6 +4770,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4804,7 +4804,7 @@
         <v>127753914</v>
       </c>
       <c r="B43" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127753906</v>
+        <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>79647</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742078</v>
+        <v>742075</v>
       </c>
       <c r="R44" t="n">
-        <v>7154651</v>
+        <v>7154759</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127753891</v>
+        <v>127753906</v>
       </c>
       <c r="B45" t="n">
-        <v>79641</v>
+        <v>57832</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742075</v>
+        <v>742078</v>
       </c>
       <c r="R45" t="n">
-        <v>7154759</v>
+        <v>7154651</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753927</v>
+        <v>127753888</v>
       </c>
       <c r="B47" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741946</v>
+        <v>742028</v>
       </c>
       <c r="R47" t="n">
-        <v>7154636</v>
+        <v>7154827</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753915</v>
+        <v>127753927</v>
       </c>
       <c r="B49" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742161</v>
+        <v>741946</v>
       </c>
       <c r="R49" t="n">
-        <v>7154587</v>
+        <v>7154636</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753888</v>
+        <v>127753915</v>
       </c>
       <c r="B50" t="n">
-        <v>79055</v>
+        <v>78787</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742028</v>
+        <v>742161</v>
       </c>
       <c r="R50" t="n">
-        <v>7154827</v>
+        <v>7154587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127753938</v>
+        <v>127753929</v>
       </c>
       <c r="B53" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741791</v>
+        <v>742148</v>
       </c>
       <c r="R53" t="n">
-        <v>7154734</v>
+        <v>7154762</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5843,11 +5843,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5874,10 +5869,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127753929</v>
+        <v>127753938</v>
       </c>
       <c r="B54" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5909,10 +5904,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>742148</v>
+        <v>741791</v>
       </c>
       <c r="R54" t="n">
-        <v>7154762</v>
+        <v>7154734</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5945,6 +5940,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5974,7 +5974,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753896</v>
+        <v>127753899</v>
       </c>
       <c r="B2" t="n">
         <v>57672</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>742082</v>
+        <v>741764</v>
       </c>
       <c r="R2" t="n">
-        <v>7154435</v>
+        <v>7154654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753899</v>
+        <v>127753896</v>
       </c>
       <c r="B3" t="n">
         <v>57672</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741764</v>
+        <v>742082</v>
       </c>
       <c r="R3" t="n">
-        <v>7154654</v>
+        <v>7154435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1199,32 +1199,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753910</v>
+        <v>127753908</v>
       </c>
       <c r="B7" t="n">
-        <v>92643</v>
+        <v>80161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742161</v>
+        <v>742037</v>
       </c>
       <c r="R7" t="n">
-        <v>7154742</v>
+        <v>7154881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,32 +1393,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753908</v>
+        <v>127753946</v>
       </c>
       <c r="B9" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742037</v>
+        <v>742105</v>
       </c>
       <c r="R9" t="n">
-        <v>7154881</v>
+        <v>7154699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1464,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,32 +1495,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753946</v>
+        <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>92644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742105</v>
+        <v>742161</v>
       </c>
       <c r="R10" t="n">
-        <v>7154699</v>
+        <v>7154742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1566,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753948</v>
+        <v>127753889</v>
       </c>
       <c r="B14" t="n">
-        <v>92639</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742148</v>
+        <v>742160</v>
       </c>
       <c r="R14" t="n">
-        <v>7154762</v>
+        <v>7154588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753889</v>
+        <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742160</v>
+        <v>741967</v>
       </c>
       <c r="R15" t="n">
-        <v>7154588</v>
+        <v>7154801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753942</v>
+        <v>127753930</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741967</v>
+        <v>742153</v>
       </c>
       <c r="R16" t="n">
-        <v>7154801</v>
+        <v>7154757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,32 +2187,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753930</v>
+        <v>127753948</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742153</v>
+        <v>742148</v>
       </c>
       <c r="R17" t="n">
-        <v>7154757</v>
+        <v>7154762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753919</v>
+        <v>127753892</v>
       </c>
       <c r="B19" t="n">
-        <v>91367</v>
+        <v>79647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742028</v>
+        <v>742068</v>
       </c>
       <c r="R19" t="n">
-        <v>7154827</v>
+        <v>7154593</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753892</v>
+        <v>127753940</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742068</v>
+        <v>741843</v>
       </c>
       <c r="R20" t="n">
-        <v>7154593</v>
+        <v>7154744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,6 +2562,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,7 +2593,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753940</v>
+        <v>127753924</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R21" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2664,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753924</v>
+        <v>127753919</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2981,45 +2981,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753949</v>
+        <v>127753902</v>
       </c>
       <c r="B25" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742157</v>
+        <v>741941</v>
       </c>
       <c r="R25" t="n">
-        <v>7154655</v>
+        <v>7154765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,6 +3060,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,53 +3091,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753902</v>
+        <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741941</v>
+        <v>742157</v>
       </c>
       <c r="R26" t="n">
-        <v>7154765</v>
+        <v>7154655</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,11 +3162,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91179</v>
+        <v>91180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127753923</v>
+        <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741996</v>
+        <v>742030</v>
       </c>
       <c r="R33" t="n">
-        <v>7154840</v>
+        <v>7154816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127753918</v>
+        <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>91367</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,21 +3887,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>742030</v>
+        <v>741996</v>
       </c>
       <c r="R34" t="n">
-        <v>7154816</v>
+        <v>7154840</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4277,45 +4277,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753947</v>
+        <v>127753939</v>
       </c>
       <c r="B38" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741968</v>
+        <v>741814</v>
       </c>
       <c r="R38" t="n">
-        <v>7154662</v>
+        <v>7154740</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4350,12 +4357,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4374,7 +4387,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753939</v>
+        <v>127753944</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4403,23 +4416,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741814</v>
+        <v>742023</v>
       </c>
       <c r="R39" t="n">
-        <v>7154740</v>
+        <v>7154856</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4454,18 +4460,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753944</v>
+        <v>127753901</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4495,34 +4495,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742023</v>
+        <v>741759</v>
       </c>
       <c r="R40" t="n">
-        <v>7154856</v>
+        <v>7154728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4555,6 +4563,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4691,53 +4704,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753901</v>
+        <v>127753947</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741759</v>
+        <v>741968</v>
       </c>
       <c r="R42" t="n">
-        <v>7154728</v>
+        <v>7154662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4770,11 +4775,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127753945</v>
+        <v>127753890</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5589,21 +5589,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742030</v>
+        <v>741905</v>
       </c>
       <c r="R51" t="n">
-        <v>7154816</v>
+        <v>7154732</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127753890</v>
+        <v>127753945</v>
       </c>
       <c r="B52" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5686,21 +5686,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741905</v>
+        <v>742030</v>
       </c>
       <c r="R52" t="n">
-        <v>7154732</v>
+        <v>7154816</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5974,7 +5974,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753899</v>
+        <v>127753896</v>
       </c>
       <c r="B2" t="n">
         <v>57672</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741764</v>
+        <v>742082</v>
       </c>
       <c r="R2" t="n">
-        <v>7154654</v>
+        <v>7154435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753896</v>
+        <v>127753899</v>
       </c>
       <c r="B3" t="n">
         <v>57672</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742082</v>
+        <v>741764</v>
       </c>
       <c r="R3" t="n">
-        <v>7154435</v>
+        <v>7154654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1199,32 +1199,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753908</v>
+        <v>127753921</v>
       </c>
       <c r="B7" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742037</v>
+        <v>742101</v>
       </c>
       <c r="R7" t="n">
-        <v>7154881</v>
+        <v>7154742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,32 +1296,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753921</v>
+        <v>127753908</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742101</v>
+        <v>742037</v>
       </c>
       <c r="R8" t="n">
-        <v>7154742</v>
+        <v>7154881</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753889</v>
+        <v>127753948</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742160</v>
+        <v>742148</v>
       </c>
       <c r="R14" t="n">
-        <v>7154588</v>
+        <v>7154762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753942</v>
+        <v>127753889</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741967</v>
+        <v>742160</v>
       </c>
       <c r="R15" t="n">
-        <v>7154801</v>
+        <v>7154588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753930</v>
+        <v>127753942</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742153</v>
+        <v>741967</v>
       </c>
       <c r="R16" t="n">
-        <v>7154757</v>
+        <v>7154801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,32 +2187,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753948</v>
+        <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742148</v>
+        <v>742153</v>
       </c>
       <c r="R17" t="n">
-        <v>7154762</v>
+        <v>7154757</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753892</v>
+        <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>79647</v>
+        <v>91368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742068</v>
+        <v>742028</v>
       </c>
       <c r="R19" t="n">
-        <v>7154593</v>
+        <v>7154827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753940</v>
+        <v>127753892</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741843</v>
+        <v>742068</v>
       </c>
       <c r="R20" t="n">
-        <v>7154744</v>
+        <v>7154593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,11 +2562,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753924</v>
+        <v>127753940</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R21" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753919</v>
+        <v>127753924</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2884,32 +2884,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127753916</v>
+        <v>127753949</v>
       </c>
       <c r="B24" t="n">
-        <v>78787</v>
+        <v>92640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>742075</v>
+        <v>742157</v>
       </c>
       <c r="R24" t="n">
-        <v>7154759</v>
+        <v>7154655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753902</v>
+        <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,42 +2992,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741941</v>
+        <v>742075</v>
       </c>
       <c r="R25" t="n">
-        <v>7154765</v>
+        <v>7154759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,11 +3052,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3091,45 +3078,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753949</v>
+        <v>127753902</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742157</v>
+        <v>741941</v>
       </c>
       <c r="R26" t="n">
-        <v>7154655</v>
+        <v>7154765</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,6 +3157,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4277,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753939</v>
+        <v>127753914</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4288,41 +4288,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741814</v>
+        <v>741905</v>
       </c>
       <c r="R38" t="n">
-        <v>7154740</v>
+        <v>7154732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4355,11 +4348,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,32 +4375,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753944</v>
+        <v>127753947</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4422,10 +4410,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>742023</v>
+        <v>741968</v>
       </c>
       <c r="R39" t="n">
-        <v>7154856</v>
+        <v>7154662</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4484,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753901</v>
+        <v>127753939</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4495,29 +4483,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4527,10 +4514,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741759</v>
+        <v>741814</v>
       </c>
       <c r="R40" t="n">
-        <v>7154728</v>
+        <v>7154740</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4554,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4576,6 +4563,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4594,10 +4582,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753893</v>
+        <v>127753944</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,42 +4593,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742157</v>
+        <v>742023</v>
       </c>
       <c r="R41" t="n">
-        <v>7154690</v>
+        <v>7154856</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4673,11 +4653,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4704,45 +4679,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753947</v>
+        <v>127753893</v>
       </c>
       <c r="B42" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741968</v>
+        <v>742157</v>
       </c>
       <c r="R42" t="n">
-        <v>7154662</v>
+        <v>7154690</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4775,6 +4758,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4801,10 +4789,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753914</v>
+        <v>127753901</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4812,34 +4800,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741905</v>
+        <v>741759</v>
       </c>
       <c r="R43" t="n">
-        <v>7154732</v>
+        <v>7154728</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4874,13 +4870,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5578,32 +5578,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127753890</v>
+        <v>127753912</v>
       </c>
       <c r="B51" t="n">
-        <v>79647</v>
+        <v>92652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>741905</v>
+        <v>742158</v>
       </c>
       <c r="R51" t="n">
-        <v>7154732</v>
+        <v>7154703</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127753929</v>
+        <v>127753890</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5783,21 +5783,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>742148</v>
+        <v>741905</v>
       </c>
       <c r="R53" t="n">
-        <v>7154762</v>
+        <v>7154732</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127753938</v>
+        <v>127753929</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741791</v>
+        <v>742148</v>
       </c>
       <c r="R54" t="n">
-        <v>7154734</v>
+        <v>7154762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,11 +5940,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5971,32 +5966,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127753912</v>
+        <v>127753938</v>
       </c>
       <c r="B55" t="n">
-        <v>92652</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6006,10 +6001,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>742158</v>
+        <v>741791</v>
       </c>
       <c r="R55" t="n">
-        <v>7154703</v>
+        <v>7154734</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6042,6 +6037,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753896</v>
+        <v>127753899</v>
       </c>
       <c r="B2" t="n">
         <v>57672</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>742082</v>
+        <v>741764</v>
       </c>
       <c r="R2" t="n">
-        <v>7154435</v>
+        <v>7154654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753899</v>
+        <v>127753896</v>
       </c>
       <c r="B3" t="n">
         <v>57672</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741764</v>
+        <v>742082</v>
       </c>
       <c r="R3" t="n">
-        <v>7154654</v>
+        <v>7154435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1199,32 +1199,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753921</v>
+        <v>127753910</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>92645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742101</v>
+        <v>742161</v>
       </c>
       <c r="R7" t="n">
         <v>7154742</v>
@@ -1296,32 +1296,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753908</v>
+        <v>127753946</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742037</v>
+        <v>742105</v>
       </c>
       <c r="R8" t="n">
-        <v>7154881</v>
+        <v>7154699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,6 +1367,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753946</v>
+        <v>127753921</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1428,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742105</v>
+        <v>742101</v>
       </c>
       <c r="R9" t="n">
-        <v>7154699</v>
+        <v>7154742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,11 +1469,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,32 +1495,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753910</v>
+        <v>127753908</v>
       </c>
       <c r="B10" t="n">
-        <v>92644</v>
+        <v>80161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742161</v>
+        <v>742037</v>
       </c>
       <c r="R10" t="n">
-        <v>7154742</v>
+        <v>7154881</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
         <v>127753948</v>
       </c>
       <c r="B14" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753942</v>
+        <v>127753900</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,34 +2101,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741967</v>
+        <v>741768</v>
       </c>
       <c r="R16" t="n">
-        <v>7154801</v>
+        <v>7154679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,6 +2169,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2187,7 +2200,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753930</v>
+        <v>127753942</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2222,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742153</v>
+        <v>741967</v>
       </c>
       <c r="R17" t="n">
-        <v>7154757</v>
+        <v>7154801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2284,10 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753900</v>
+        <v>127753930</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,42 +2308,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741768</v>
+        <v>742153</v>
       </c>
       <c r="R18" t="n">
-        <v>7154679</v>
+        <v>7154757</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,11 +2368,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,7 +2397,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753892</v>
+        <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742068</v>
+        <v>742028</v>
       </c>
       <c r="R20" t="n">
-        <v>7154593</v>
+        <v>7154827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753940</v>
+        <v>127753943</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741843</v>
+        <v>742046</v>
       </c>
       <c r="R21" t="n">
-        <v>7154744</v>
+        <v>7154883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753924</v>
+        <v>127753940</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R22" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753943</v>
+        <v>127753892</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742046</v>
+        <v>742068</v>
       </c>
       <c r="R23" t="n">
-        <v>7154883</v>
+        <v>7154593</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>127753949</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91180</v>
+        <v>91181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753926</v>
+        <v>127753928</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741971</v>
+        <v>741972</v>
       </c>
       <c r="R28" t="n">
-        <v>7154589</v>
+        <v>7154672</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753922</v>
+        <v>127753937</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741952</v>
+        <v>741770</v>
       </c>
       <c r="R29" t="n">
-        <v>7154778</v>
+        <v>7154740</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127753937</v>
+        <v>127753922</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741770</v>
+        <v>741952</v>
       </c>
       <c r="R31" t="n">
-        <v>7154740</v>
+        <v>7154778</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127753928</v>
+        <v>127753926</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741972</v>
+        <v>741971</v>
       </c>
       <c r="R32" t="n">
-        <v>7154672</v>
+        <v>7154589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127753918</v>
+        <v>127753923</v>
       </c>
       <c r="B33" t="n">
-        <v>91368</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>742030</v>
+        <v>741996</v>
       </c>
       <c r="R33" t="n">
-        <v>7154816</v>
+        <v>7154840</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127753923</v>
+        <v>127753918</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>91369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,21 +3887,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741996</v>
+        <v>742030</v>
       </c>
       <c r="R34" t="n">
-        <v>7154840</v>
+        <v>7154816</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4378,7 +4378,7 @@
         <v>127753947</v>
       </c>
       <c r="B39" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753939</v>
+        <v>127753944</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4501,23 +4501,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741814</v>
+        <v>742023</v>
       </c>
       <c r="R40" t="n">
-        <v>7154740</v>
+        <v>7154856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4552,18 +4545,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4582,7 +4569,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753944</v>
+        <v>127753939</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4611,16 +4598,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742023</v>
+        <v>741814</v>
       </c>
       <c r="R41" t="n">
-        <v>7154856</v>
+        <v>7154740</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,12 +4649,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753888</v>
+        <v>127753917</v>
       </c>
       <c r="B47" t="n">
-        <v>79061</v>
+        <v>78787</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742028</v>
+        <v>742091</v>
       </c>
       <c r="R47" t="n">
-        <v>7154827</v>
+        <v>7154655</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753917</v>
+        <v>127753888</v>
       </c>
       <c r="B48" t="n">
-        <v>78787</v>
+        <v>79061</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742091</v>
+        <v>742028</v>
       </c>
       <c r="R48" t="n">
-        <v>7154655</v>
+        <v>7154827</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
         <v>127753912</v>
       </c>
       <c r="B51" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127753890</v>
+        <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5783,21 +5783,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741905</v>
+        <v>741791</v>
       </c>
       <c r="R53" t="n">
-        <v>7154732</v>
+        <v>7154734</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5843,6 +5843,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5966,10 +5971,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127753938</v>
+        <v>127753890</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5977,21 +5982,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6001,10 +6006,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741791</v>
+        <v>741905</v>
       </c>
       <c r="R55" t="n">
-        <v>7154734</v>
+        <v>7154732</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6037,11 +6042,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753899</v>
+        <v>127753903</v>
       </c>
       <c r="B2" t="n">
         <v>57672</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741764</v>
+        <v>741967</v>
       </c>
       <c r="R2" t="n">
-        <v>7154654</v>
+        <v>7154801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753896</v>
+        <v>127753899</v>
       </c>
       <c r="B3" t="n">
         <v>57672</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742082</v>
+        <v>741764</v>
       </c>
       <c r="R3" t="n">
-        <v>7154435</v>
+        <v>7154654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753903</v>
+        <v>127753896</v>
       </c>
       <c r="B4" t="n">
         <v>57672</v>
@@ -928,7 +928,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741967</v>
+        <v>742082</v>
       </c>
       <c r="R4" t="n">
-        <v>7154801</v>
+        <v>7154435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1199,32 +1199,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753910</v>
+        <v>127753921</v>
       </c>
       <c r="B7" t="n">
-        <v>92645</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742161</v>
+        <v>742101</v>
       </c>
       <c r="R7" t="n">
         <v>7154742</v>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753921</v>
+        <v>127753910</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>92646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742101</v>
+        <v>742161</v>
       </c>
       <c r="R9" t="n">
         <v>7154742</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753936</v>
+        <v>127753894</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,34 +1700,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741761</v>
+        <v>742156</v>
       </c>
       <c r="R12" t="n">
-        <v>7154695</v>
+        <v>7154631</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1768,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753894</v>
+        <v>127753936</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,42 +1810,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742156</v>
+        <v>741761</v>
       </c>
       <c r="R13" t="n">
-        <v>7154631</v>
+        <v>7154695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,11 +1870,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753948</v>
+        <v>127753889</v>
       </c>
       <c r="B14" t="n">
-        <v>92641</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742148</v>
+        <v>742160</v>
       </c>
       <c r="R14" t="n">
-        <v>7154762</v>
+        <v>7154588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753889</v>
+        <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742160</v>
+        <v>741967</v>
       </c>
       <c r="R15" t="n">
-        <v>7154588</v>
+        <v>7154801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753900</v>
+        <v>127753930</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,42 +2101,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741768</v>
+        <v>742153</v>
       </c>
       <c r="R16" t="n">
-        <v>7154679</v>
+        <v>7154757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,11 +2161,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753942</v>
+        <v>127753900</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,34 +2198,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741967</v>
+        <v>741768</v>
       </c>
       <c r="R17" t="n">
-        <v>7154801</v>
+        <v>7154679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,6 +2266,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,32 +2297,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753930</v>
+        <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742153</v>
+        <v>742148</v>
       </c>
       <c r="R18" t="n">
-        <v>7154757</v>
+        <v>7154762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753924</v>
+        <v>127753892</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742028</v>
+        <v>742068</v>
       </c>
       <c r="R20" t="n">
-        <v>7154827</v>
+        <v>7154593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753943</v>
+        <v>127753940</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742046</v>
+        <v>741843</v>
       </c>
       <c r="R21" t="n">
-        <v>7154883</v>
+        <v>7154744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,7 +2690,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753940</v>
+        <v>127753924</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R22" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2761,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753892</v>
+        <v>127753943</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742068</v>
+        <v>742046</v>
       </c>
       <c r="R23" t="n">
-        <v>7154593</v>
+        <v>7154883</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>127753949</v>
       </c>
       <c r="B24" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91181</v>
+        <v>91182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753928</v>
+        <v>127753926</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741972</v>
+        <v>741971</v>
       </c>
       <c r="R28" t="n">
-        <v>7154672</v>
+        <v>7154589</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753937</v>
+        <v>127753922</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741770</v>
+        <v>741952</v>
       </c>
       <c r="R29" t="n">
-        <v>7154740</v>
+        <v>7154778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127753922</v>
+        <v>127753937</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741952</v>
+        <v>741770</v>
       </c>
       <c r="R31" t="n">
-        <v>7154778</v>
+        <v>7154740</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127753926</v>
+        <v>127753928</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741971</v>
+        <v>741972</v>
       </c>
       <c r="R32" t="n">
-        <v>7154589</v>
+        <v>7154672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127753923</v>
+        <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741996</v>
+        <v>742030</v>
       </c>
       <c r="R33" t="n">
-        <v>7154840</v>
+        <v>7154816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127753918</v>
+        <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>91369</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,21 +3887,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>742030</v>
+        <v>741996</v>
       </c>
       <c r="R34" t="n">
-        <v>7154816</v>
+        <v>7154840</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753914</v>
+        <v>127753893</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4288,34 +4288,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741905</v>
+        <v>742157</v>
       </c>
       <c r="R38" t="n">
-        <v>7154732</v>
+        <v>7154690</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4350,13 +4358,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4375,32 +4387,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753947</v>
+        <v>127753914</v>
       </c>
       <c r="B39" t="n">
-        <v>92641</v>
+        <v>78788</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4410,10 +4422,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741968</v>
+        <v>741905</v>
       </c>
       <c r="R39" t="n">
-        <v>7154662</v>
+        <v>7154732</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4454,6 +4466,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4472,32 +4485,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753944</v>
+        <v>127753947</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4507,10 +4520,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742023</v>
+        <v>741968</v>
       </c>
       <c r="R40" t="n">
-        <v>7154856</v>
+        <v>7154662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4679,10 +4692,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753893</v>
+        <v>127753944</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,42 +4703,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>742157</v>
+        <v>742023</v>
       </c>
       <c r="R42" t="n">
-        <v>7154690</v>
+        <v>7154856</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4758,11 +4763,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753917</v>
+        <v>127753888</v>
       </c>
       <c r="B47" t="n">
-        <v>78787</v>
+        <v>79061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742091</v>
+        <v>742028</v>
       </c>
       <c r="R47" t="n">
-        <v>7154655</v>
+        <v>7154827</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753888</v>
+        <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>79061</v>
+        <v>78787</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742028</v>
+        <v>742091</v>
       </c>
       <c r="R48" t="n">
-        <v>7154827</v>
+        <v>7154655</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
         <v>127753912</v>
       </c>
       <c r="B51" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127753938</v>
+        <v>127753890</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5783,21 +5783,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741791</v>
+        <v>741905</v>
       </c>
       <c r="R53" t="n">
-        <v>7154734</v>
+        <v>7154732</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5843,11 +5843,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5971,10 +5966,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127753890</v>
+        <v>127753938</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5982,21 +5977,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6006,10 +6001,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741905</v>
+        <v>741791</v>
       </c>
       <c r="R55" t="n">
-        <v>7154732</v>
+        <v>7154734</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6042,6 +6037,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753903</v>
+        <v>127753899</v>
       </c>
       <c r="B2" t="n">
         <v>57672</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741967</v>
+        <v>741764</v>
       </c>
       <c r="R2" t="n">
-        <v>7154801</v>
+        <v>7154654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753899</v>
+        <v>127753896</v>
       </c>
       <c r="B3" t="n">
         <v>57672</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741764</v>
+        <v>742082</v>
       </c>
       <c r="R3" t="n">
-        <v>7154654</v>
+        <v>7154435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753896</v>
+        <v>127753903</v>
       </c>
       <c r="B4" t="n">
         <v>57672</v>
@@ -928,7 +928,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742082</v>
+        <v>741967</v>
       </c>
       <c r="R4" t="n">
-        <v>7154435</v>
+        <v>7154801</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1199,32 +1199,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753921</v>
+        <v>127753910</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>92646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742101</v>
+        <v>742161</v>
       </c>
       <c r="R7" t="n">
         <v>7154742</v>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753910</v>
+        <v>127753921</v>
       </c>
       <c r="B9" t="n">
-        <v>92646</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742161</v>
+        <v>742101</v>
       </c>
       <c r="R9" t="n">
         <v>7154742</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753894</v>
+        <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,42 +1700,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742156</v>
+        <v>741761</v>
       </c>
       <c r="R12" t="n">
-        <v>7154631</v>
+        <v>7154695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753936</v>
+        <v>127753894</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,34 +1797,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741761</v>
+        <v>742156</v>
       </c>
       <c r="R13" t="n">
-        <v>7154695</v>
+        <v>7154631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,6 +1865,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753889</v>
+        <v>127753948</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742160</v>
+        <v>742148</v>
       </c>
       <c r="R14" t="n">
-        <v>7154588</v>
+        <v>7154762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753900</v>
+        <v>127753889</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,42 +2198,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741768</v>
+        <v>742160</v>
       </c>
       <c r="R17" t="n">
-        <v>7154679</v>
+        <v>7154588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,11 +2258,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,45 +2284,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753948</v>
+        <v>127753900</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742148</v>
+        <v>741768</v>
       </c>
       <c r="R18" t="n">
-        <v>7154762</v>
+        <v>7154679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,6 +2363,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753919</v>
+        <v>127753924</v>
       </c>
       <c r="B19" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753892</v>
+        <v>127753919</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742068</v>
+        <v>742028</v>
       </c>
       <c r="R20" t="n">
-        <v>7154593</v>
+        <v>7154827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,7 +2690,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753924</v>
+        <v>127753943</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742028</v>
+        <v>742046</v>
       </c>
       <c r="R22" t="n">
-        <v>7154827</v>
+        <v>7154883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753943</v>
+        <v>127753892</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742046</v>
+        <v>742068</v>
       </c>
       <c r="R23" t="n">
-        <v>7154883</v>
+        <v>7154593</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753926</v>
+        <v>127753928</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741971</v>
+        <v>741972</v>
       </c>
       <c r="R28" t="n">
-        <v>7154589</v>
+        <v>7154672</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753922</v>
+        <v>127753937</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741952</v>
+        <v>741770</v>
       </c>
       <c r="R29" t="n">
-        <v>7154778</v>
+        <v>7154740</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127753937</v>
+        <v>127753922</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741770</v>
+        <v>741952</v>
       </c>
       <c r="R31" t="n">
-        <v>7154740</v>
+        <v>7154778</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127753928</v>
+        <v>127753926</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741972</v>
+        <v>741971</v>
       </c>
       <c r="R32" t="n">
-        <v>7154672</v>
+        <v>7154589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127753918</v>
+        <v>127753923</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>742030</v>
+        <v>741996</v>
       </c>
       <c r="R33" t="n">
-        <v>7154816</v>
+        <v>7154840</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127753923</v>
+        <v>127753918</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,21 +3887,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741996</v>
+        <v>742030</v>
       </c>
       <c r="R34" t="n">
-        <v>7154840</v>
+        <v>7154816</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753934</v>
+        <v>127753904</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,34 +3984,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741961</v>
+        <v>741989</v>
       </c>
       <c r="R35" t="n">
-        <v>7154435</v>
+        <v>7154834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4044,6 +4052,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4070,10 +4083,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753904</v>
+        <v>127753934</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4081,42 +4094,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741989</v>
+        <v>741961</v>
       </c>
       <c r="R36" t="n">
-        <v>7154834</v>
+        <v>7154435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4149,11 +4154,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4277,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753893</v>
+        <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4288,42 +4288,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>742157</v>
+        <v>742023</v>
       </c>
       <c r="R38" t="n">
-        <v>7154690</v>
+        <v>7154856</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4356,11 +4348,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753914</v>
+        <v>127753901</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4398,34 +4385,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741905</v>
+        <v>741759</v>
       </c>
       <c r="R39" t="n">
-        <v>7154732</v>
+        <v>7154728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4460,13 +4455,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4485,45 +4484,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753947</v>
+        <v>127753893</v>
       </c>
       <c r="B40" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741968</v>
+        <v>742157</v>
       </c>
       <c r="R40" t="n">
-        <v>7154662</v>
+        <v>7154690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4556,6 +4563,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4582,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753939</v>
+        <v>127753914</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4593,41 +4605,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741814</v>
+        <v>741905</v>
       </c>
       <c r="R41" t="n">
-        <v>7154740</v>
+        <v>7154732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,11 +4665,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4692,32 +4692,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753944</v>
+        <v>127753947</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>742023</v>
+        <v>741968</v>
       </c>
       <c r="R42" t="n">
-        <v>7154856</v>
+        <v>7154662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753901</v>
+        <v>127753939</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4800,29 +4800,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4832,10 +4831,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741759</v>
+        <v>741814</v>
       </c>
       <c r="R43" t="n">
-        <v>7154728</v>
+        <v>7154740</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4881,6 +4880,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753917</v>
+        <v>127753927</v>
       </c>
       <c r="B48" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742091</v>
+        <v>741946</v>
       </c>
       <c r="R48" t="n">
-        <v>7154655</v>
+        <v>7154636</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753927</v>
+        <v>127753917</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>741946</v>
+        <v>742091</v>
       </c>
       <c r="R49" t="n">
-        <v>7154636</v>
+        <v>7154655</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127753929</v>
+        <v>127753938</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>742148</v>
+        <v>741791</v>
       </c>
       <c r="R54" t="n">
-        <v>7154762</v>
+        <v>7154734</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,6 +5940,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5966,7 +5971,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127753938</v>
+        <v>127753929</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6001,10 +6006,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741791</v>
+        <v>742148</v>
       </c>
       <c r="R55" t="n">
-        <v>7154734</v>
+        <v>7154762</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6037,11 +6042,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753930</v>
+        <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742153</v>
+        <v>742160</v>
       </c>
       <c r="R16" t="n">
-        <v>7154757</v>
+        <v>7154588</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753889</v>
+        <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742160</v>
+        <v>742153</v>
       </c>
       <c r="R17" t="n">
-        <v>7154588</v>
+        <v>7154757</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753924</v>
+        <v>127753940</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R19" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,6 +2465,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753919</v>
+        <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2507,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2588,7 +2593,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753940</v>
+        <v>127753943</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741843</v>
+        <v>742046</v>
       </c>
       <c r="R21" t="n">
-        <v>7154744</v>
+        <v>7154883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2664,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753943</v>
+        <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742046</v>
+        <v>742068</v>
       </c>
       <c r="R22" t="n">
-        <v>7154883</v>
+        <v>7154593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753892</v>
+        <v>127753919</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742068</v>
+        <v>742028</v>
       </c>
       <c r="R23" t="n">
-        <v>7154593</v>
+        <v>7154827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753901</v>
+        <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,29 +4385,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4417,10 +4416,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741759</v>
+        <v>741814</v>
       </c>
       <c r="R39" t="n">
-        <v>7154728</v>
+        <v>7154740</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4457,7 +4456,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4466,6 +4465,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753893</v>
+        <v>127753901</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4517,7 +4517,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742157</v>
+        <v>741759</v>
       </c>
       <c r="R40" t="n">
-        <v>7154690</v>
+        <v>7154728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753914</v>
+        <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,34 +4605,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741905</v>
+        <v>742157</v>
       </c>
       <c r="R41" t="n">
-        <v>7154732</v>
+        <v>7154690</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4667,13 +4675,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4789,10 +4801,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753939</v>
+        <v>127753914</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4800,41 +4812,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741814</v>
+        <v>741905</v>
       </c>
       <c r="R43" t="n">
-        <v>7154740</v>
+        <v>7154732</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,11 +4872,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753889</v>
+        <v>127753930</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742160</v>
+        <v>742153</v>
       </c>
       <c r="R16" t="n">
-        <v>7154588</v>
+        <v>7154757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753930</v>
+        <v>127753889</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742153</v>
+        <v>742160</v>
       </c>
       <c r="R17" t="n">
-        <v>7154757</v>
+        <v>7154588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753940</v>
+        <v>127753924</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R19" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,11 +2465,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753924</v>
+        <v>127753919</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753943</v>
+        <v>127753940</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742046</v>
+        <v>741843</v>
       </c>
       <c r="R21" t="n">
-        <v>7154883</v>
+        <v>7154744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753892</v>
+        <v>127753943</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742068</v>
+        <v>742046</v>
       </c>
       <c r="R22" t="n">
-        <v>7154593</v>
+        <v>7154883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753919</v>
+        <v>127753892</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742028</v>
+        <v>742068</v>
       </c>
       <c r="R23" t="n">
-        <v>7154827</v>
+        <v>7154593</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753939</v>
+        <v>127753901</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,28 +4385,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4416,10 +4417,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741814</v>
+        <v>741759</v>
       </c>
       <c r="R39" t="n">
-        <v>7154740</v>
+        <v>7154728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4456,7 +4457,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4465,7 +4466,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753901</v>
+        <v>127753893</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4517,7 +4517,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741759</v>
+        <v>742157</v>
       </c>
       <c r="R40" t="n">
-        <v>7154728</v>
+        <v>7154690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753893</v>
+        <v>127753914</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,42 +4605,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742157</v>
+        <v>741905</v>
       </c>
       <c r="R41" t="n">
-        <v>7154690</v>
+        <v>7154732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4675,17 +4667,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4801,10 +4789,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753914</v>
+        <v>127753939</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4812,34 +4800,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741905</v>
+        <v>741814</v>
       </c>
       <c r="R43" t="n">
-        <v>7154732</v>
+        <v>7154740</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4872,6 +4867,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -2394,7 +2394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753924</v>
+        <v>127753940</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R19" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,6 +2465,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753919</v>
+        <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2507,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2588,7 +2593,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753940</v>
+        <v>127753943</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741843</v>
+        <v>742046</v>
       </c>
       <c r="R21" t="n">
-        <v>7154744</v>
+        <v>7154883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2664,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753943</v>
+        <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742046</v>
+        <v>742068</v>
       </c>
       <c r="R22" t="n">
-        <v>7154883</v>
+        <v>7154593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753892</v>
+        <v>127753919</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742068</v>
+        <v>742028</v>
       </c>
       <c r="R23" t="n">
-        <v>7154593</v>
+        <v>7154827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753904</v>
+        <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,42 +3984,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741989</v>
+        <v>741961</v>
       </c>
       <c r="R35" t="n">
-        <v>7154834</v>
+        <v>7154435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,11 +4044,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4083,10 +4070,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753934</v>
+        <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,34 +4081,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741961</v>
+        <v>741989</v>
       </c>
       <c r="R36" t="n">
-        <v>7154435</v>
+        <v>7154834</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4154,6 +4149,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753901</v>
+        <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,29 +4385,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4417,10 +4416,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741759</v>
+        <v>741814</v>
       </c>
       <c r="R39" t="n">
-        <v>7154728</v>
+        <v>7154740</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4457,7 +4456,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4466,6 +4465,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753893</v>
+        <v>127753901</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4517,7 +4517,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742157</v>
+        <v>741759</v>
       </c>
       <c r="R40" t="n">
-        <v>7154690</v>
+        <v>7154728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753914</v>
+        <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,34 +4605,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741905</v>
+        <v>742157</v>
       </c>
       <c r="R41" t="n">
-        <v>7154732</v>
+        <v>7154690</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4667,13 +4675,17 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4789,10 +4801,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753939</v>
+        <v>127753914</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4800,41 +4812,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741814</v>
+        <v>741905</v>
       </c>
       <c r="R43" t="n">
-        <v>7154740</v>
+        <v>7154732</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,11 +4872,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753930</v>
+        <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742153</v>
+        <v>742160</v>
       </c>
       <c r="R16" t="n">
-        <v>7154757</v>
+        <v>7154588</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753889</v>
+        <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742160</v>
+        <v>742153</v>
       </c>
       <c r="R17" t="n">
-        <v>7154588</v>
+        <v>7154757</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753934</v>
+        <v>127753904</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,34 +3984,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741961</v>
+        <v>741989</v>
       </c>
       <c r="R35" t="n">
-        <v>7154435</v>
+        <v>7154834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4044,6 +4052,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4070,10 +4083,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753904</v>
+        <v>127753934</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4081,42 +4094,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741989</v>
+        <v>741961</v>
       </c>
       <c r="R36" t="n">
-        <v>7154834</v>
+        <v>7154435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4149,11 +4154,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753889</v>
+        <v>127753930</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742160</v>
+        <v>742153</v>
       </c>
       <c r="R16" t="n">
-        <v>7154588</v>
+        <v>7154757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753930</v>
+        <v>127753889</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742153</v>
+        <v>742160</v>
       </c>
       <c r="R17" t="n">
-        <v>7154757</v>
+        <v>7154588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753940</v>
+        <v>127753924</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741843</v>
+        <v>742028</v>
       </c>
       <c r="R19" t="n">
-        <v>7154744</v>
+        <v>7154827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,11 +2465,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753924</v>
+        <v>127753919</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753943</v>
+        <v>127753940</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742046</v>
+        <v>741843</v>
       </c>
       <c r="R21" t="n">
-        <v>7154883</v>
+        <v>7154744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753892</v>
+        <v>127753943</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742068</v>
+        <v>742046</v>
       </c>
       <c r="R22" t="n">
-        <v>7154593</v>
+        <v>7154883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753919</v>
+        <v>127753892</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742028</v>
+        <v>742068</v>
       </c>
       <c r="R23" t="n">
-        <v>7154827</v>
+        <v>7154593</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753930</v>
+        <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742153</v>
+        <v>742160</v>
       </c>
       <c r="R16" t="n">
-        <v>7154757</v>
+        <v>7154588</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753889</v>
+        <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742160</v>
+        <v>742153</v>
       </c>
       <c r="R17" t="n">
-        <v>7154588</v>
+        <v>7154757</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753904</v>
+        <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,42 +3984,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741989</v>
+        <v>741961</v>
       </c>
       <c r="R35" t="n">
-        <v>7154834</v>
+        <v>7154435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,11 +4044,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4083,10 +4070,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753934</v>
+        <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,34 +4081,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741961</v>
+        <v>741989</v>
       </c>
       <c r="R36" t="n">
-        <v>7154435</v>
+        <v>7154834</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4154,6 +4149,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753939</v>
+        <v>127753901</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4385,28 +4385,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4416,10 +4417,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741814</v>
+        <v>741759</v>
       </c>
       <c r="R39" t="n">
-        <v>7154740</v>
+        <v>7154728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4456,7 +4457,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4465,7 +4466,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753901</v>
+        <v>127753893</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4517,7 +4517,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741759</v>
+        <v>742157</v>
       </c>
       <c r="R40" t="n">
-        <v>7154728</v>
+        <v>7154690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753893</v>
+        <v>127753914</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,42 +4605,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742157</v>
+        <v>741905</v>
       </c>
       <c r="R41" t="n">
-        <v>7154690</v>
+        <v>7154732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4675,17 +4667,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4801,10 +4789,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753914</v>
+        <v>127753939</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4812,34 +4800,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741905</v>
+        <v>741814</v>
       </c>
       <c r="R43" t="n">
-        <v>7154732</v>
+        <v>7154740</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4872,6 +4867,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753899</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127753896</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127753903</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>127753910</v>
       </c>
       <c r="B7" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127753946</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>127753921</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>127753908</v>
       </c>
       <c r="B10" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>127753887</v>
       </c>
       <c r="B11" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753936</v>
+        <v>127753894</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,34 +1700,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741761</v>
+        <v>742156</v>
       </c>
       <c r="R12" t="n">
-        <v>7154695</v>
+        <v>7154631</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1768,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753894</v>
+        <v>127753936</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,42 +1810,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742156</v>
+        <v>741761</v>
       </c>
       <c r="R13" t="n">
-        <v>7154631</v>
+        <v>7154695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,11 +1870,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,7 +1899,7 @@
         <v>127753948</v>
       </c>
       <c r="B14" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127753900</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127753924</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753919</v>
+        <v>127753943</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742028</v>
+        <v>742046</v>
       </c>
       <c r="R20" t="n">
-        <v>7154827</v>
+        <v>7154883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753940</v>
+        <v>127753892</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741843</v>
+        <v>742068</v>
       </c>
       <c r="R21" t="n">
-        <v>7154744</v>
+        <v>7154593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753943</v>
+        <v>127753940</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742046</v>
+        <v>741843</v>
       </c>
       <c r="R22" t="n">
-        <v>7154883</v>
+        <v>7154744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753892</v>
+        <v>127753919</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>91378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742068</v>
+        <v>742028</v>
       </c>
       <c r="R23" t="n">
-        <v>7154593</v>
+        <v>7154827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>127753949</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>127753902</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91182</v>
+        <v>91191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>127753923</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>127753918</v>
       </c>
       <c r="B34" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753934</v>
+        <v>127753904</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,34 +3984,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741961</v>
+        <v>741989</v>
       </c>
       <c r="R35" t="n">
-        <v>7154435</v>
+        <v>7154834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4044,6 +4052,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4070,10 +4083,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753904</v>
+        <v>127753934</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4081,42 +4094,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741989</v>
+        <v>741961</v>
       </c>
       <c r="R36" t="n">
-        <v>7154834</v>
+        <v>7154435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4149,11 +4154,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,7 +4183,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753944</v>
+        <v>127753901</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4288,34 +4288,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>742023</v>
+        <v>741759</v>
       </c>
       <c r="R38" t="n">
-        <v>7154856</v>
+        <v>7154728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,6 +4356,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,10 +4387,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753901</v>
+        <v>127753893</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4407,7 +4420,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4417,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741759</v>
+        <v>742157</v>
       </c>
       <c r="R39" t="n">
-        <v>7154728</v>
+        <v>7154690</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4457,7 +4470,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4484,53 +4497,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753893</v>
+        <v>127753947</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742157</v>
+        <v>741968</v>
       </c>
       <c r="R40" t="n">
-        <v>7154690</v>
+        <v>7154662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,11 +4568,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753914</v>
+        <v>127753944</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741905</v>
+        <v>742023</v>
       </c>
       <c r="R41" t="n">
-        <v>7154732</v>
+        <v>7154856</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4673,7 +4673,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4692,45 +4691,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753947</v>
+        <v>127753939</v>
       </c>
       <c r="B42" t="n">
-        <v>92642</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741968</v>
+        <v>741814</v>
       </c>
       <c r="R42" t="n">
-        <v>7154662</v>
+        <v>7154740</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,12 +4771,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4789,10 +4801,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753939</v>
+        <v>127753914</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4800,41 +4812,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741814</v>
+        <v>741905</v>
       </c>
       <c r="R43" t="n">
-        <v>7154740</v>
+        <v>7154732</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,11 +4872,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4899,10 +4899,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127753891</v>
+        <v>127753906</v>
       </c>
       <c r="B44" t="n">
-        <v>79647</v>
+        <v>57833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742075</v>
+        <v>742078</v>
       </c>
       <c r="R44" t="n">
-        <v>7154759</v>
+        <v>7154651</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127753906</v>
+        <v>127753891</v>
       </c>
       <c r="B45" t="n">
-        <v>57832</v>
+        <v>79650</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742078</v>
+        <v>742075</v>
       </c>
       <c r="R45" t="n">
-        <v>7154651</v>
+        <v>7154759</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753888</v>
+        <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742028</v>
+        <v>741946</v>
       </c>
       <c r="R47" t="n">
-        <v>7154827</v>
+        <v>7154636</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753927</v>
+        <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741946</v>
+        <v>742091</v>
       </c>
       <c r="R48" t="n">
-        <v>7154636</v>
+        <v>7154655</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753917</v>
+        <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742091</v>
+        <v>742161</v>
       </c>
       <c r="R49" t="n">
-        <v>7154655</v>
+        <v>7154587</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753915</v>
+        <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>78787</v>
+        <v>79064</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742161</v>
+        <v>742028</v>
       </c>
       <c r="R50" t="n">
-        <v>7154587</v>
+        <v>7154827</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
         <v>127753912</v>
       </c>
       <c r="B51" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127753945</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>127753890</v>
       </c>
       <c r="B53" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>127753938</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>127753929</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753948</v>
+        <v>127753942</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742148</v>
+        <v>741967</v>
       </c>
       <c r="R14" t="n">
-        <v>7154762</v>
+        <v>7154801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753942</v>
+        <v>127753889</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741967</v>
+        <v>742160</v>
       </c>
       <c r="R15" t="n">
-        <v>7154801</v>
+        <v>7154588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753889</v>
+        <v>127753930</v>
       </c>
       <c r="B16" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742160</v>
+        <v>742153</v>
       </c>
       <c r="R16" t="n">
-        <v>7154588</v>
+        <v>7154757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753930</v>
+        <v>127753900</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,34 +2198,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742153</v>
+        <v>741768</v>
       </c>
       <c r="R17" t="n">
-        <v>7154757</v>
+        <v>7154679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,6 +2266,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,53 +2297,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753900</v>
+        <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741768</v>
+        <v>742148</v>
       </c>
       <c r="R18" t="n">
-        <v>7154679</v>
+        <v>7154762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,11 +2368,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4277,53 +4277,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753901</v>
+        <v>127753947</v>
       </c>
       <c r="B38" t="n">
-        <v>57673</v>
+        <v>92650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741759</v>
+        <v>741968</v>
       </c>
       <c r="R38" t="n">
-        <v>7154728</v>
+        <v>7154662</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4356,11 +4348,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753893</v>
+        <v>127753944</v>
       </c>
       <c r="B39" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4398,42 +4385,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>742157</v>
+        <v>742023</v>
       </c>
       <c r="R39" t="n">
-        <v>7154690</v>
+        <v>7154856</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,11 +4445,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4497,45 +4471,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753947</v>
+        <v>127753939</v>
       </c>
       <c r="B40" t="n">
-        <v>92650</v>
+        <v>79032</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741968</v>
+        <v>741814</v>
       </c>
       <c r="R40" t="n">
-        <v>7154662</v>
+        <v>7154740</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4570,12 +4551,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4594,10 +4581,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753944</v>
+        <v>127753901</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,34 +4592,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742023</v>
+        <v>741759</v>
       </c>
       <c r="R41" t="n">
-        <v>7154856</v>
+        <v>7154728</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4660,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4691,10 +4691,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753939</v>
+        <v>127753893</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4702,28 +4702,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4733,10 +4734,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741814</v>
+        <v>742157</v>
       </c>
       <c r="R42" t="n">
-        <v>7154740</v>
+        <v>7154690</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4773,7 +4774,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4782,7 +4783,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753927</v>
+        <v>127753888</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79064</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741946</v>
+        <v>742028</v>
       </c>
       <c r="R47" t="n">
-        <v>7154636</v>
+        <v>7154827</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753917</v>
+        <v>127753927</v>
       </c>
       <c r="B48" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742091</v>
+        <v>741946</v>
       </c>
       <c r="R48" t="n">
-        <v>7154655</v>
+        <v>7154636</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753915</v>
+        <v>127753917</v>
       </c>
       <c r="B49" t="n">
         <v>78790</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742161</v>
+        <v>742091</v>
       </c>
       <c r="R49" t="n">
-        <v>7154587</v>
+        <v>7154655</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753888</v>
+        <v>127753915</v>
       </c>
       <c r="B50" t="n">
-        <v>79064</v>
+        <v>78790</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742028</v>
+        <v>742161</v>
       </c>
       <c r="R50" t="n">
-        <v>7154827</v>
+        <v>7154587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753899</v>
+        <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741764</v>
+        <v>742082</v>
       </c>
       <c r="R2" t="n">
-        <v>7154654</v>
+        <v>7154435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753896</v>
+        <v>127753903</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742082</v>
+        <v>741967</v>
       </c>
       <c r="R3" t="n">
-        <v>7154435</v>
+        <v>7154801</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753903</v>
+        <v>127753899</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741967</v>
+        <v>741764</v>
       </c>
       <c r="R4" t="n">
-        <v>7154801</v>
+        <v>7154654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1008,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,32 +1199,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753910</v>
+        <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>92654</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742161</v>
+        <v>742105</v>
       </c>
       <c r="R7" t="n">
-        <v>7154742</v>
+        <v>7154699</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753946</v>
+        <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742105</v>
+        <v>742101</v>
       </c>
       <c r="R8" t="n">
-        <v>7154699</v>
+        <v>7154742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753921</v>
+        <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>80217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742101</v>
+        <v>742037</v>
       </c>
       <c r="R9" t="n">
-        <v>7154742</v>
+        <v>7154881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,32 +1495,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753908</v>
+        <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>80164</v>
+        <v>92746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742037</v>
+        <v>742161</v>
       </c>
       <c r="R10" t="n">
-        <v>7154881</v>
+        <v>7154742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753887</v>
+        <v>127753894</v>
       </c>
       <c r="B11" t="n">
-        <v>79064</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,34 +1603,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741864</v>
+        <v>742156</v>
       </c>
       <c r="R11" t="n">
-        <v>7154736</v>
+        <v>7154631</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1671,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1702,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753894</v>
+        <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,42 +1713,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742156</v>
+        <v>741761</v>
       </c>
       <c r="R12" t="n">
-        <v>7154631</v>
+        <v>7154695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,11 +1773,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753936</v>
+        <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741761</v>
+        <v>741864</v>
       </c>
       <c r="R13" t="n">
-        <v>7154695</v>
+        <v>7154736</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753942</v>
+        <v>127753900</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,34 +1907,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741967</v>
+        <v>741768</v>
       </c>
       <c r="R14" t="n">
-        <v>7154801</v>
+        <v>7154679</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1993,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753889</v>
+        <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742160</v>
+        <v>741967</v>
       </c>
       <c r="R15" t="n">
-        <v>7154588</v>
+        <v>7154801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753930</v>
+        <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742153</v>
+        <v>742160</v>
       </c>
       <c r="R16" t="n">
-        <v>7154757</v>
+        <v>7154588</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753900</v>
+        <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,42 +2211,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741768</v>
+        <v>742153</v>
       </c>
       <c r="R17" t="n">
-        <v>7154679</v>
+        <v>7154757</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,11 +2271,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2300,7 +2300,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753924</v>
+        <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753943</v>
+        <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742046</v>
+        <v>742028</v>
       </c>
       <c r="R20" t="n">
-        <v>7154883</v>
+        <v>7154827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753892</v>
+        <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742068</v>
+        <v>742046</v>
       </c>
       <c r="R21" t="n">
-        <v>7154593</v>
+        <v>7154883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753940</v>
+        <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741843</v>
+        <v>742068</v>
       </c>
       <c r="R22" t="n">
-        <v>7154744</v>
+        <v>7154593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2756,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753919</v>
+        <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742028</v>
+        <v>741843</v>
       </c>
       <c r="R23" t="n">
-        <v>7154827</v>
+        <v>7154744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2853,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,45 +2884,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127753949</v>
+        <v>127753902</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>742157</v>
+        <v>741941</v>
       </c>
       <c r="R24" t="n">
-        <v>7154655</v>
+        <v>7154765</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2963,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,7 +2997,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,53 +3091,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753902</v>
+        <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741941</v>
+        <v>742157</v>
       </c>
       <c r="R26" t="n">
-        <v>7154765</v>
+        <v>7154655</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,11 +3162,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3191,7 +3191,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91191</v>
+        <v>91283</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127753923</v>
+        <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741996</v>
+        <v>742030</v>
       </c>
       <c r="R33" t="n">
-        <v>7154840</v>
+        <v>7154816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127753918</v>
+        <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,21 +3887,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>742030</v>
+        <v>741996</v>
       </c>
       <c r="R34" t="n">
-        <v>7154816</v>
+        <v>7154840</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753904</v>
+        <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,42 +3984,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741989</v>
+        <v>741961</v>
       </c>
       <c r="R35" t="n">
-        <v>7154834</v>
+        <v>7154435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,11 +4044,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4083,10 +4070,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753934</v>
+        <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,34 +4081,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741961</v>
+        <v>741989</v>
       </c>
       <c r="R36" t="n">
-        <v>7154435</v>
+        <v>7154834</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4154,6 +4149,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,7 +4183,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4277,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753947</v>
+        <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>92650</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741968</v>
+        <v>742023</v>
       </c>
       <c r="R38" t="n">
-        <v>7154662</v>
+        <v>7154856</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753944</v>
+        <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4403,16 +4403,23 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>742023</v>
+        <v>741814</v>
       </c>
       <c r="R39" t="n">
-        <v>7154856</v>
+        <v>7154740</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4447,12 +4454,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4471,10 +4484,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753939</v>
+        <v>127753901</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4482,28 +4495,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4513,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741814</v>
+        <v>741759</v>
       </c>
       <c r="R40" t="n">
-        <v>7154740</v>
+        <v>7154728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4553,7 +4567,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4562,7 +4576,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4581,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753901</v>
+        <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4614,7 +4627,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4624,10 +4637,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741759</v>
+        <v>742157</v>
       </c>
       <c r="R41" t="n">
-        <v>7154728</v>
+        <v>7154690</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4664,7 +4677,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4691,10 +4704,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753893</v>
+        <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>78841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4702,42 +4715,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>742157</v>
+        <v>741905</v>
       </c>
       <c r="R42" t="n">
-        <v>7154690</v>
+        <v>7154732</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4772,17 +4777,13 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4801,32 +4802,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753914</v>
+        <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>92742</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4836,10 +4837,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741905</v>
+        <v>741968</v>
       </c>
       <c r="R43" t="n">
-        <v>7154732</v>
+        <v>7154662</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4880,7 +4881,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127753906</v>
+        <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>57833</v>
+        <v>79702</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742078</v>
+        <v>742075</v>
       </c>
       <c r="R44" t="n">
-        <v>7154651</v>
+        <v>7154759</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127753891</v>
+        <v>127753906</v>
       </c>
       <c r="B45" t="n">
-        <v>79650</v>
+        <v>57845</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742075</v>
+        <v>742078</v>
       </c>
       <c r="R45" t="n">
-        <v>7154759</v>
+        <v>7154651</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753888</v>
+        <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79064</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742028</v>
+        <v>741946</v>
       </c>
       <c r="R47" t="n">
-        <v>7154827</v>
+        <v>7154636</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753927</v>
+        <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>78840</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741946</v>
+        <v>742091</v>
       </c>
       <c r="R48" t="n">
-        <v>7154636</v>
+        <v>7154655</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753917</v>
+        <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742091</v>
+        <v>742161</v>
       </c>
       <c r="R49" t="n">
-        <v>7154655</v>
+        <v>7154587</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753915</v>
+        <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>78790</v>
+        <v>79115</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742161</v>
+        <v>742028</v>
       </c>
       <c r="R50" t="n">
-        <v>7154587</v>
+        <v>7154827</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,32 +5578,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127753912</v>
+        <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>92662</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742158</v>
+        <v>742030</v>
       </c>
       <c r="R51" t="n">
-        <v>7154703</v>
+        <v>7154816</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127753945</v>
+        <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5686,21 +5686,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>742030</v>
+        <v>741905</v>
       </c>
       <c r="R52" t="n">
-        <v>7154816</v>
+        <v>7154732</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127753890</v>
+        <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5783,21 +5783,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741905</v>
+        <v>741791</v>
       </c>
       <c r="R53" t="n">
-        <v>7154732</v>
+        <v>7154734</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5843,6 +5843,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5869,10 +5874,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127753938</v>
+        <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5904,10 +5909,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741791</v>
+        <v>742148</v>
       </c>
       <c r="R54" t="n">
-        <v>7154734</v>
+        <v>7154762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5940,11 +5945,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5971,32 +5971,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127753929</v>
+        <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>92754</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>742148</v>
+        <v>742158</v>
       </c>
       <c r="R55" t="n">
-        <v>7154762</v>
+        <v>7154703</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,14 +781,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127753903</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,14 +895,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127753899</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,14 +1009,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,14 +1110,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,14 +1211,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,14 +1317,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,14 +1418,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>80254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,14 +1519,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92746</v>
+        <v>92798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,14 +1620,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127753894</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,14 +1734,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,14 +1835,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
+        <v>79152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,14 +1936,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127753900</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,14 +2050,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,14 +2151,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79702</v>
+        <v>79739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,14 +2252,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,14 +2353,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,14 +2454,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91470</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,14 +2555,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,14 +2656,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2681,14 +2757,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79702</v>
+        <v>79739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2778,14 +2858,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2880,14 +2964,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127753902</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2990,14 +3078,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78840</v>
+        <v>78877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3087,14 +3179,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3184,14 +3280,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91283</v>
+        <v>91335</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,14 +3390,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,14 +3491,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3484,14 +3592,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,14 +3693,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3678,14 +3794,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3775,14 +3895,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91470</v>
+        <v>91522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,14 +3996,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,14 +4097,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,14 +4198,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,14 +4312,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4273,14 +4413,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4370,14 +4514,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4480,14 +4628,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>127753901</v>
       </c>
       <c r="B40" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,14 +4742,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,14 +4856,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78841</v>
+        <v>78878</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4798,14 +4958,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4895,14 +5059,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79702</v>
+        <v>79739</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,14 +5160,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>127753906</v>
       </c>
       <c r="B45" t="n">
-        <v>57845</v>
+        <v>57876</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5089,14 +5261,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5186,14 +5362,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5283,14 +5463,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78840</v>
+        <v>78877</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5380,14 +5564,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78840</v>
+        <v>78877</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5477,14 +5665,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79115</v>
+        <v>79152</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5574,14 +5766,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5671,14 +5867,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79702</v>
+        <v>79739</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5768,14 +5968,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5870,14 +6074,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5967,14 +6175,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92754</v>
+        <v>92806</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6064,7 +6276,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127753903</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127753899</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127753894</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>127753900</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127753902</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91335</v>
+        <v>91339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>127753901</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>127753906</v>
       </c>
       <c r="B45" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127753903</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127753899</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127753894</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>127753900</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127753902</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91339</v>
+        <v>91344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>127753901</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>127753906</v>
       </c>
       <c r="B45" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91351</v>
+        <v>91354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91354</v>
+        <v>91357</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127753903</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127753899</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127753894</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>127753900</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127753902</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91357</v>
+        <v>91363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>127753901</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>127753906</v>
       </c>
       <c r="B45" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91363</v>
+        <v>91370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753896</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127753903</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127753899</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127753894</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>127753900</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>127753902</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127753904</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>127753901</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>127753893</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>127753906</v>
       </c>
       <c r="B45" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91372</v>
+        <v>91371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2482,14 +2482,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3190,7 +3186,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3906,7 +3902,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3923,14 +3919,10 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4969,7 +4961,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5272,7 +5264,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6186,7 +6178,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91371</v>
+        <v>91374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>127753935</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127753931</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>127753946</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>127753921</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>127753908</v>
       </c>
       <c r="B9" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753936</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>127753887</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>127753942</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127753889</v>
       </c>
       <c r="B16" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>127753930</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>127753924</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127753943</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>127753892</v>
       </c>
       <c r="B22" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>127753940</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>127753916</v>
       </c>
       <c r="B25" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91374</v>
+        <v>91376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>127753928</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>127753937</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>127753932</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>127753922</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127753926</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>127753923</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127753934</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>127753941</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>127753944</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>127753939</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>127753914</v>
       </c>
       <c r="B42" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>127753891</v>
       </c>
       <c r="B44" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>127753927</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>127753917</v>
       </c>
       <c r="B48" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127753915</v>
       </c>
       <c r="B49" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>127753888</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>127753945</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>127753890</v>
       </c>
       <c r="B52" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>127753938</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>127753929</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -1530,7 +1530,7 @@
         <v>127753910</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127753948</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>127753919</v>
       </c>
       <c r="B19" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127753949</v>
       </c>
       <c r="B26" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>127753913</v>
       </c>
       <c r="B27" t="n">
-        <v>91376</v>
+        <v>91380</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127753918</v>
       </c>
       <c r="B33" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>127753947</v>
       </c>
       <c r="B43" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>127753950</v>
       </c>
       <c r="B46" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>127753912</v>
       </c>
       <c r="B55" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753896</v>
+        <v>127753887</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>742082</v>
+        <v>741864</v>
       </c>
       <c r="R2" t="n">
-        <v>7154435</v>
+        <v>7154736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753903</v>
+        <v>127753888</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,42 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741967</v>
+        <v>742028</v>
       </c>
       <c r="R3" t="n">
-        <v>7154801</v>
+        <v>7154827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +847,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753899</v>
+        <v>127753947</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741764</v>
+        <v>741968</v>
       </c>
       <c r="R4" t="n">
-        <v>7154654</v>
+        <v>7154662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127753935</v>
+        <v>127753948</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741943</v>
+        <v>742148</v>
       </c>
       <c r="R5" t="n">
-        <v>7154464</v>
+        <v>7154762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753931</v>
+        <v>127753949</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742161</v>
+        <v>742157</v>
       </c>
       <c r="R6" t="n">
-        <v>7154617</v>
+        <v>7154655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753946</v>
+        <v>127753950</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742105</v>
+        <v>741946</v>
       </c>
       <c r="R7" t="n">
-        <v>7154699</v>
+        <v>7154636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753921</v>
+        <v>127753910</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1316,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742101</v>
+        <v>742161</v>
       </c>
       <c r="R8" t="n">
         <v>7154742</v>
@@ -1426,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753908</v>
+        <v>127753911</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>93201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742037</v>
+        <v>742163</v>
       </c>
       <c r="R9" t="n">
-        <v>7154881</v>
+        <v>7154588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753910</v>
+        <v>127753912</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742161</v>
+        <v>742158</v>
       </c>
       <c r="R10" t="n">
-        <v>7154742</v>
+        <v>7154703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753894</v>
+        <v>127753913</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>91738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,31 +1595,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1671,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>742156</v>
+        <v>742030</v>
       </c>
       <c r="R11" t="n">
-        <v>7154631</v>
+        <v>7154816</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1662,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På död granticka. Säregen doft, likt kokad frukt. T.ex. som när man kokar jordgubbssylt. Sparar kollekt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,6 +1671,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,14 +1694,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753936</v>
+        <v>127753921</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1777,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741761</v>
+        <v>742101</v>
       </c>
       <c r="R12" t="n">
-        <v>7154695</v>
+        <v>7154742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,32 +1795,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753887</v>
+        <v>127753922</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741864</v>
+        <v>741952</v>
       </c>
       <c r="R13" t="n">
-        <v>7154736</v>
+        <v>7154778</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,53 +1896,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753900</v>
+        <v>127753923</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741768</v>
+        <v>741996</v>
       </c>
       <c r="R14" t="n">
-        <v>7154679</v>
+        <v>7154840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,11 +1967,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,14 +1997,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753942</v>
+        <v>127753924</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2093,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741967</v>
+        <v>742028</v>
       </c>
       <c r="R15" t="n">
-        <v>7154801</v>
+        <v>7154827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,32 +2098,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753889</v>
+        <v>127753926</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742160</v>
+        <v>741971</v>
       </c>
       <c r="R16" t="n">
-        <v>7154588</v>
+        <v>7154589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,14 +2199,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753930</v>
+        <v>127753927</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2295,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742153</v>
+        <v>741946</v>
       </c>
       <c r="R17" t="n">
-        <v>7154757</v>
+        <v>7154636</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,32 +2300,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753948</v>
+        <v>127753928</v>
       </c>
       <c r="B18" t="n">
-        <v>92831</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2396,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742148</v>
+        <v>741972</v>
       </c>
       <c r="R18" t="n">
-        <v>7154762</v>
+        <v>7154672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,30 +2401,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753919</v>
+        <v>127753929</v>
       </c>
       <c r="B19" t="n">
-        <v>91569</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2493,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742028</v>
+        <v>742148</v>
       </c>
       <c r="R19" t="n">
-        <v>7154827</v>
+        <v>7154762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,14 +2502,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753924</v>
+        <v>127753930</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2594,10 +2537,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742028</v>
+        <v>742153</v>
       </c>
       <c r="R20" t="n">
-        <v>7154827</v>
+        <v>7154757</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,14 +2603,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753943</v>
+        <v>127753931</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2695,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742046</v>
+        <v>742161</v>
       </c>
       <c r="R21" t="n">
-        <v>7154883</v>
+        <v>7154617</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,32 +2704,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753892</v>
+        <v>127753932</v>
       </c>
       <c r="B22" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2796,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>742068</v>
+        <v>742064</v>
       </c>
       <c r="R22" t="n">
-        <v>7154593</v>
+        <v>7154419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,14 +2805,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753940</v>
+        <v>127753933</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2897,10 +2840,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741843</v>
+        <v>741989</v>
       </c>
       <c r="R23" t="n">
-        <v>7154744</v>
+        <v>7154414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,11 +2876,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2968,53 +2906,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127753902</v>
+        <v>127753934</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741941</v>
+        <v>741961</v>
       </c>
       <c r="R24" t="n">
-        <v>7154765</v>
+        <v>7154435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,11 +2977,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3082,32 +3007,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753916</v>
+        <v>127753935</v>
       </c>
       <c r="B25" t="n">
-        <v>78801</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3117,10 +3042,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742075</v>
+        <v>741943</v>
       </c>
       <c r="R25" t="n">
-        <v>7154759</v>
+        <v>7154464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,32 +3108,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753949</v>
+        <v>127753936</v>
       </c>
       <c r="B26" t="n">
-        <v>92831</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3218,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742157</v>
+        <v>741761</v>
       </c>
       <c r="R26" t="n">
-        <v>7154655</v>
+        <v>7154695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3284,48 +3209,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127753913</v>
+        <v>127753937</v>
       </c>
       <c r="B27" t="n">
-        <v>91380</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6020</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742030</v>
+        <v>741770</v>
       </c>
       <c r="R27" t="n">
-        <v>7154816</v>
+        <v>7154740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,18 +3282,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På död granticka. Säregen doft, likt kokad frukt. T.ex. som när man kokar jordgubbssylt. Sparar kollekt</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3394,14 +3310,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753928</v>
+        <v>127753938</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3429,10 +3345,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741972</v>
+        <v>741791</v>
       </c>
       <c r="R28" t="n">
-        <v>7154672</v>
+        <v>7154734</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3465,6 +3381,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt, bild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3495,14 +3416,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753937</v>
+        <v>127753939</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3524,13 +3445,20 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741770</v>
+        <v>741814</v>
       </c>
       <c r="R29" t="n">
         <v>7154740</v>
@@ -3568,12 +3496,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3596,14 +3530,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127753932</v>
+        <v>127753940</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3631,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>742064</v>
+        <v>741843</v>
       </c>
       <c r="R30" t="n">
-        <v>7154419</v>
+        <v>7154744</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,6 +3601,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3697,14 +3636,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127753922</v>
+        <v>127753941</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3732,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741952</v>
+        <v>741864</v>
       </c>
       <c r="R31" t="n">
-        <v>7154778</v>
+        <v>7154736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3798,14 +3737,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127753926</v>
+        <v>127753942</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3833,10 +3772,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741971</v>
+        <v>741967</v>
       </c>
       <c r="R32" t="n">
-        <v>7154589</v>
+        <v>7154801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3899,30 +3838,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127753918</v>
+        <v>127753943</v>
       </c>
       <c r="B33" t="n">
-        <v>91569</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3930,10 +3873,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>742030</v>
+        <v>742046</v>
       </c>
       <c r="R33" t="n">
-        <v>7154816</v>
+        <v>7154883</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3996,14 +3939,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127753923</v>
+        <v>127753944</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4031,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741996</v>
+        <v>742023</v>
       </c>
       <c r="R34" t="n">
-        <v>7154840</v>
+        <v>7154856</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4097,14 +4040,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127753934</v>
+        <v>127753945</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4132,10 +4075,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741961</v>
+        <v>742030</v>
       </c>
       <c r="R35" t="n">
-        <v>7154435</v>
+        <v>7154816</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4198,53 +4141,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127753904</v>
+        <v>127753946</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741989</v>
+        <v>742105</v>
       </c>
       <c r="R36" t="n">
-        <v>7154834</v>
+        <v>7154699</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,7 +4216,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4312,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127753941</v>
+        <v>127753915</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4323,21 +4258,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4347,10 +4282,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741864</v>
+        <v>742161</v>
       </c>
       <c r="R37" t="n">
-        <v>7154736</v>
+        <v>7154587</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4413,10 +4348,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127753944</v>
+        <v>127753916</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4424,21 +4359,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4448,10 +4383,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>742023</v>
+        <v>742075</v>
       </c>
       <c r="R38" t="n">
-        <v>7154856</v>
+        <v>7154759</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4514,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127753939</v>
+        <v>127753917</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4525,41 +4460,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741814</v>
+        <v>742091</v>
       </c>
       <c r="R39" t="n">
-        <v>7154740</v>
+        <v>7154655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,18 +4522,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4628,10 +4550,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127753901</v>
+        <v>127753889</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4639,42 +4561,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741759</v>
+        <v>742160</v>
       </c>
       <c r="R40" t="n">
-        <v>7154728</v>
+        <v>7154588</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,11 +4621,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4742,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127753893</v>
+        <v>127753890</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4753,42 +4662,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742157</v>
+        <v>741905</v>
       </c>
       <c r="R41" t="n">
-        <v>7154690</v>
+        <v>7154732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4821,11 +4722,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4856,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127753914</v>
+        <v>127753891</v>
       </c>
       <c r="B42" t="n">
-        <v>78802</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4867,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4891,10 +4787,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741905</v>
+        <v>742075</v>
       </c>
       <c r="R42" t="n">
-        <v>7154732</v>
+        <v>7154759</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4935,7 +4831,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4958,32 +4853,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127753947</v>
+        <v>127753892</v>
       </c>
       <c r="B43" t="n">
-        <v>92831</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4993,10 +4888,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741968</v>
+        <v>742068</v>
       </c>
       <c r="R43" t="n">
-        <v>7154662</v>
+        <v>7154593</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5059,32 +4954,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127753891</v>
+        <v>127753908</v>
       </c>
       <c r="B44" t="n">
-        <v>79663</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5094,10 +4989,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742075</v>
+        <v>742037</v>
       </c>
       <c r="R44" t="n">
-        <v>7154759</v>
+        <v>7154881</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5160,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127753906</v>
+        <v>127753893</v>
       </c>
       <c r="B45" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5171,34 +5066,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742078</v>
+        <v>742157</v>
       </c>
       <c r="R45" t="n">
-        <v>7154651</v>
+        <v>7154690</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5231,6 +5134,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5261,45 +5169,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127753950</v>
+        <v>127753894</v>
       </c>
       <c r="B46" t="n">
-        <v>92831</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>741946</v>
+        <v>742156</v>
       </c>
       <c r="R46" t="n">
-        <v>7154636</v>
+        <v>7154631</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5332,6 +5248,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5362,10 +5283,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127753927</v>
+        <v>127753895</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5373,34 +5294,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741946</v>
+        <v>742164</v>
       </c>
       <c r="R47" t="n">
-        <v>7154636</v>
+        <v>7154590</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5433,6 +5362,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5463,10 +5397,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127753917</v>
+        <v>127753896</v>
       </c>
       <c r="B48" t="n">
-        <v>78801</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5474,34 +5408,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742091</v>
+        <v>742082</v>
       </c>
       <c r="R48" t="n">
-        <v>7154655</v>
+        <v>7154435</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,6 +5476,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5564,10 +5511,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127753915</v>
+        <v>127753898</v>
       </c>
       <c r="B49" t="n">
-        <v>78801</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5575,34 +5522,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742161</v>
+        <v>741783</v>
       </c>
       <c r="R49" t="n">
-        <v>7154587</v>
+        <v>7154637</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5635,6 +5590,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5665,10 +5625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127753888</v>
+        <v>127753899</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5676,34 +5636,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742028</v>
+        <v>741764</v>
       </c>
       <c r="R50" t="n">
-        <v>7154827</v>
+        <v>7154654</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5736,6 +5704,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5766,10 +5739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127753945</v>
+        <v>127753900</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5777,34 +5750,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742030</v>
+        <v>741768</v>
       </c>
       <c r="R51" t="n">
-        <v>7154816</v>
+        <v>7154679</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5837,6 +5818,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5867,10 +5853,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127753890</v>
+        <v>127753901</v>
       </c>
       <c r="B52" t="n">
-        <v>79663</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5878,34 +5864,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741905</v>
+        <v>741759</v>
       </c>
       <c r="R52" t="n">
-        <v>7154732</v>
+        <v>7154728</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5938,6 +5932,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5968,10 +5967,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127753938</v>
+        <v>127753902</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5979,34 +5978,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741791</v>
+        <v>741941</v>
       </c>
       <c r="R53" t="n">
-        <v>7154734</v>
+        <v>7154765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6043,7 +6050,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt, bild</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6074,10 +6081,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127753929</v>
+        <v>127753903</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6085,34 +6092,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>742148</v>
+        <v>741967</v>
       </c>
       <c r="R54" t="n">
-        <v>7154762</v>
+        <v>7154801</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6145,6 +6160,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6175,45 +6195,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127753912</v>
+        <v>127753904</v>
       </c>
       <c r="B55" t="n">
-        <v>92843</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rundaberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>742158</v>
+        <v>741989</v>
       </c>
       <c r="R55" t="n">
-        <v>7154703</v>
+        <v>7154834</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6248,6 +6276,11 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6269,6 +6302,310 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127753906</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Rundaberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>742078</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7154651</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127753907</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Rundaberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>742134</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7154485</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127753914</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Rundaberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>741905</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7154732</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 35963-2025 artfynd.xlsx
+++ b/artfynd/A 35963-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753887</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753949</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753950</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753910</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753911</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1579,6 +1624,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753912</t>
         </is>
       </c>
     </row>
@@ -1691,6 +1741,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753913</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1792,6 +1847,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753921</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753922</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753923</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753924</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753926</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2297,6 +2377,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753927</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2398,6 +2483,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753928</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2499,6 +2589,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753929</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753930</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753931</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2802,6 +2907,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753932</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2903,6 +3013,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753933</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,6 +3119,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753934</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3105,6 +3225,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753935</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3206,6 +3331,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753936</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753937</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3413,6 +3548,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753938</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753939</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3633,6 +3778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753940</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3734,6 +3884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753941</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3835,6 +3990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753942</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753943</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4037,6 +4202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753944</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4138,6 +4308,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753945</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4244,6 +4419,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753946</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4345,6 +4525,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753915</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753916</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4547,6 +4737,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753917</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4648,6 +4843,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753889</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4749,6 +4949,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753890</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4850,6 +5055,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753891</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4951,6 +5161,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753892</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5052,6 +5267,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753908</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5166,6 +5386,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753893</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5280,6 +5505,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753894</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5394,6 +5624,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753895</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5508,6 +5743,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753896</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5622,6 +5862,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753898</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5736,6 +5981,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753899</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5850,6 +6100,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753900</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5964,6 +6219,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753901</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6078,6 +6338,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753902</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6192,6 +6457,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753903</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6306,6 +6576,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753904</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6407,6 +6682,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753906</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6508,6 +6788,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753907</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6610,8 +6895,72 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753914</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>